--- a/data/trans_dic/P17G_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico privado en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a privado/a (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,82</t>
+          <t>0,3; 1,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,6</t>
+          <t>0,29; 1,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,02</t>
+          <t>0,07; 1,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,14</t>
+          <t>0,47; 2,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,4</t>
+          <t>0,14; 1,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,23</t>
+          <t>1,0; 3,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,2</t>
+          <t>0,31; 1,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,21</t>
+          <t>0,34; 1,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,29</t>
+          <t>0,3; 1,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,02</t>
+          <t>0,81; 2,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,86</t>
+          <t>0,26; 0,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,2</t>
+          <t>0,54; 2,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,41</t>
+          <t>0,57; 2,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,46</t>
+          <t>1,38; 3,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,02</t>
+          <t>0,78; 2,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,37</t>
+          <t>1,27; 3,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,5</t>
+          <t>0,84; 2,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,13</t>
+          <t>0,62; 2,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,6</t>
+          <t>1,19; 2,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,35</t>
+          <t>1,07; 2,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,05</t>
+          <t>0,87; 2,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,48</t>
+          <t>1,25; 2,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,49</t>
+          <t>1,12; 2,45</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,08</t>
+          <t>1,27; 3,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,76</t>
+          <t>0,67; 2,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,35</t>
+          <t>0,47; 2,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,17</t>
+          <t>1,18; 4,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,48</t>
+          <t>1,12; 3,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,87</t>
+          <t>0,39; 1,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,86</t>
+          <t>0,92; 2,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,26</t>
+          <t>0,99; 3,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,98</t>
+          <t>1,52; 3,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,87</t>
+          <t>0,73; 2,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,25</t>
+          <t>0,9; 2,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,1</t>
+          <t>1,31; 2,96</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,85</t>
+          <t>1,12; 2,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,54</t>
+          <t>0,73; 2,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,89</t>
+          <t>1,64; 3,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,27</t>
+          <t>1,41; 3,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,06</t>
+          <t>0,75; 2,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,97</t>
+          <t>1,04; 2,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,82</t>
+          <t>1,62; 3,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,71</t>
+          <t>2,55; 4,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,2</t>
+          <t>1,09; 2,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,29</t>
+          <t>1,14; 2,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,49</t>
+          <t>1,96; 3,48</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,68</t>
+          <t>2,3; 3,74</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,88</t>
+          <t>1,03; 1,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,36</t>
+          <t>1,37; 2,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,33</t>
+          <t>1,26; 2,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,12</t>
+          <t>1,27; 2,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,66</t>
+          <t>0,9; 1,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,47</t>
+          <t>1,4; 2,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,62</t>
+          <t>1,68; 2,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,84</t>
+          <t>1,23; 1,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,61</t>
+          <t>1,02; 1,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,23</t>
+          <t>1,52; 2,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,31</t>
+          <t>1,62; 2,35</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico privado en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a privado/a (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 7811</t>
+          <t>0; 5912</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2128; 12747</t>
+          <t>2127; 13079</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1909; 10750</t>
+          <t>1962; 11449</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>456; 6482</t>
+          <t>453; 7256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3549; 14719</t>
+          <t>3247; 15161</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>993; 9670</t>
+          <t>994; 8752</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6188; 21576</t>
+          <t>6673; 22241</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2197; 8067</t>
+          <t>2115; 7832</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5052; 16779</t>
+          <t>4752; 17434</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5105; 17978</t>
+          <t>4208; 16489</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9886; 26993</t>
+          <t>10841; 29398</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3436; 11208</t>
+          <t>3460; 11443</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6048; 21091</t>
+          <t>5219; 20902</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6385; 24377</t>
+          <t>5806; 24153</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14219; 35208</t>
+          <t>14018; 35112</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9991; 36082</t>
+          <t>9275; 34873</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12265; 32600</t>
+          <t>12265; 32012</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8865; 25673</t>
+          <t>8563; 25000</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6971; 22080</t>
+          <t>6412; 22390</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11265; 24928</t>
+          <t>11354; 24901</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20600; 45357</t>
+          <t>20658; 45886</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18537; 41844</t>
+          <t>17739; 42268</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24366; 50867</t>
+          <t>25735; 50534</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>24158; 53625</t>
+          <t>23990; 52761</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9192; 27627</t>
+          <t>8590; 25331</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5919; 20736</t>
+          <t>5059; 20212</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3657; 17855</t>
+          <t>3596; 17591</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8821; 29352</t>
+          <t>8277; 29065</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7842; 23794</t>
+          <t>7666; 23441</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2863; 14455</t>
+          <t>2998; 14852</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7426; 22397</t>
+          <t>7158; 22150</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9667; 30462</t>
+          <t>9257; 29293</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19479; 40497</t>
+          <t>20672; 41194</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10257; 28498</t>
+          <t>11090; 30623</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14036; 34611</t>
+          <t>13875; 34353</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21520; 50796</t>
+          <t>21431; 48440</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10088; 26788</t>
+          <t>10549; 27821</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7641; 23814</t>
+          <t>6872; 22622</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15717; 36411</t>
+          <t>15336; 35981</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12783; 30293</t>
+          <t>13023; 30328</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7180; 21403</t>
+          <t>7818; 22368</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11057; 30849</t>
+          <t>10769; 29957</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17845; 39618</t>
+          <t>16787; 39301</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28252; 51540</t>
+          <t>27913; 51176</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21314; 43525</t>
+          <t>21637; 44050</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21908; 45319</t>
+          <t>22473; 45247</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39248; 68800</t>
+          <t>38666; 68723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46050; 74402</t>
+          <t>46423; 75462</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33859; 61432</t>
+          <t>33614; 62190</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31342; 60654</t>
+          <t>31422; 60509</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45609; 79830</t>
+          <t>46226; 76927</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>42980; 80472</t>
+          <t>43574; 80559</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>41338; 71712</t>
+          <t>42750; 74119</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>32042; 58504</t>
+          <t>31770; 61314</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51758; 86960</t>
+          <t>49277; 84521</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>61378; 95841</t>
+          <t>61488; 97143</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>83093; 122514</t>
+          <t>81811; 123182</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70533; 111291</t>
+          <t>70865; 110733</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>104946; 153876</t>
+          <t>105130; 150567</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>112788; 164489</t>
+          <t>115007; 167168</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P17G_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,87</t>
+          <t>0,29; 1,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,14</t>
+          <t>0,07; 1,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,2</t>
+          <t>0,53; 2,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,27</t>
+          <t>0,14; 1,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,33</t>
+          <t>0,96; 3,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,16</t>
+          <t>0,31; 1,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,26</t>
+          <t>0,33; 1,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,19</t>
+          <t>0,3; 1,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,2</t>
+          <t>0,82; 2,1</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,87</t>
+          <t>0,25; 0,84</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,18</t>
+          <t>0,6; 2,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,38</t>
+          <t>0,64; 2,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,45</t>
+          <t>1,35; 3,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,92</t>
+          <t>1,36; 3,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,31</t>
+          <t>1,28; 3,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,44</t>
+          <t>0,86; 2,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,16</t>
+          <t>0,66; 2,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,6</t>
+          <t>1,12; 2,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,38</t>
+          <t>1,09; 2,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,07</t>
+          <t>0,88; 2,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,46</t>
+          <t>1,24; 2,57</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,45</t>
+          <t>1,42; 2,71</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,74</t>
+          <t>1,33; 3,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,69</t>
+          <t>0,68; 2,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,32</t>
+          <t>0,44; 2,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,13</t>
+          <t>1,2; 3,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,43</t>
+          <t>1,08; 3,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,92</t>
+          <t>0,37; 1,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,83</t>
+          <t>1,04; 2,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,14</t>
+          <t>1,84; 3,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,03</t>
+          <t>1,45; 3,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,01</t>
+          <t>0,72; 1,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,23</t>
+          <t>0,9; 2,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,96</t>
+          <t>1,74; 3,34</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,96</t>
+          <t>1,07; 2,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,41</t>
+          <t>0,81; 2,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,84</t>
+          <t>1,8; 3,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,27</t>
+          <t>1,38; 3,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,16</t>
+          <t>0,72; 2,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,88</t>
+          <t>1,05; 2,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,79</t>
+          <t>1,69; 3,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,68</t>
+          <t>2,78; 4,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,23</t>
+          <t>1,08; 2,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,29</t>
+          <t>1,09; 2,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,48</t>
+          <t>1,92; 3,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,74</t>
+          <t>2,3; 3,77</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,9</t>
+          <t>1,05; 1,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,78</t>
+          <t>0,92; 1,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,27</t>
+          <t>1,39; 2,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,33</t>
+          <t>1,36; 2,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,19</t>
+          <t>1,22; 2,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,74</t>
+          <t>0,86; 1,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,4</t>
+          <t>1,43; 2,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,66</t>
+          <t>1,88; 2,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,85</t>
+          <t>1,26; 1,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,6</t>
+          <t>0,99; 1,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,18</t>
+          <t>1,54; 2,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,35</t>
+          <t>1,75; 2,41</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2262</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6837</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5912</t>
+          <t>0; 6803</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2127; 13079</t>
+          <t>2046; 13245</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1962; 11449</t>
+          <t>1942; 11430</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>453; 7256</t>
+          <t>451; 6971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3247; 15161</t>
+          <t>3625; 14795</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>994; 8752</t>
+          <t>987; 8159</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6673; 22241</t>
+          <t>6416; 22035</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2115; 7832</t>
+          <t>2261; 8090</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4752; 17434</t>
+          <t>4610; 17558</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4208; 16489</t>
+          <t>4099; 16800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10841; 29398</t>
+          <t>10948; 28115</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3460; 11443</t>
+          <t>3569; 11979</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21228</t>
+          <t>23057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17136</t>
+          <t>18169</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38364</t>
+          <t>41227</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5219; 20902</t>
+          <t>5766; 20733</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5806; 24153</t>
+          <t>6497; 25945</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14018; 35112</t>
+          <t>13694; 34787</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9275; 34873</t>
+          <t>14238; 37422</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12265; 32012</t>
+          <t>12351; 32122</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8563; 25000</t>
+          <t>8825; 24662</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6412; 22390</t>
+          <t>6811; 23010</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11354; 24901</t>
+          <t>11973; 26777</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20658; 45886</t>
+          <t>21092; 44506</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17739; 42268</t>
+          <t>17995; 42067</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25735; 50534</t>
+          <t>25401; 52734</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23990; 52761</t>
+          <t>29995; 57373</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19033</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34973</t>
+          <t>38632</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8590; 25331</t>
+          <t>9023; 26295</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5059; 20212</t>
+          <t>5079; 20301</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3596; 17591</t>
+          <t>3316; 17497</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8277; 29065</t>
+          <t>9643; 30846</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7666; 23441</t>
+          <t>7402; 22250</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2998; 14852</t>
+          <t>2854; 14969</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7158; 22150</t>
+          <t>8138; 23188</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9257; 29293</t>
+          <t>14915; 30961</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20672; 41194</t>
+          <t>19761; 41742</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11090; 30623</t>
+          <t>10954; 30160</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13875; 34353</t>
+          <t>13825; 32814</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21431; 48440</t>
+          <t>28019; 53916</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19976</t>
+          <t>21352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38824</t>
+          <t>41320</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58801</t>
+          <t>62672</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10549; 27821</t>
+          <t>10037; 27318</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6872; 22622</t>
+          <t>7598; 22693</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15336; 35981</t>
+          <t>16858; 36907</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13023; 30328</t>
+          <t>13634; 32314</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7818; 22368</t>
+          <t>7451; 22278</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10769; 29957</t>
+          <t>10880; 29168</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16787; 39301</t>
+          <t>17530; 40215</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27913; 51176</t>
+          <t>31029; 55242</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21637; 44050</t>
+          <t>21318; 44572</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22473; 45247</t>
+          <t>21627; 45230</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38666; 68723</t>
+          <t>37973; 68545</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>46423; 75462</t>
+          <t>48409; 79450</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>64044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>79255</t>
+          <t>85324</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>138661</t>
+          <t>149368</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33614; 62190</t>
+          <t>34362; 63320</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31422; 60509</t>
+          <t>31284; 61554</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46226; 76927</t>
+          <t>46905; 80693</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43574; 80559</t>
+          <t>47851; 85395</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42750; 74119</t>
+          <t>41285; 70942</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31770; 61314</t>
+          <t>30292; 57277</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>49277; 84521</t>
+          <t>50316; 83512</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>61488; 97143</t>
+          <t>69989; 104437</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81811; 123182</t>
+          <t>83428; 124147</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70865; 110733</t>
+          <t>68540; 107747</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>105130; 150567</t>
+          <t>106017; 150857</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>115007; 167168</t>
+          <t>127400; 174814</t>
         </is>
       </c>
     </row>
